--- a/data/trans_dic/P79$recibos_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P79$recibos_2023-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 8,34</t>
+          <t>0,63; 6,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 9,19</t>
+          <t>0,62; 5,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,94</t>
+          <t>0,82; 4,01</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,87</t>
+          <t>2,52; 7,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 6,41</t>
+          <t>3,23; 6,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,09</t>
+          <t>3,25; 6,07</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,39</t>
+          <t>1,51; 5,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 8,71</t>
+          <t>3,63; 7,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,13</t>
+          <t>2,98; 6,05</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 9,94</t>
+          <t>3,1; 9,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 9,41</t>
+          <t>4,5; 10,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 8,25</t>
+          <t>4,58; 9,37</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,27</t>
+          <t>0,37; 2,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,2</t>
+          <t>0,3; 1,55</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,82; 6,46</t>
+          <t>2,46; 7,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,53</t>
+          <t>3,29; 8,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,94</t>
+          <t>3,58; 7,16</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,22</t>
+          <t>1,62; 4,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,89</t>
+          <t>4,57; 8,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,03</t>
+          <t>3,59; 5,91</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,86; 26,82</t>
+          <t>22,98; 29,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24,43; 30,39</t>
+          <t>24,29; 29,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,69; 27,42</t>
+          <t>24,44; 28,44</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,82; 8,6</t>
+          <t>7,65; 9,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,17; 9,77</t>
+          <t>8,95; 10,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,99; 8,98</t>
+          <t>8,54; 9,94</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>11762</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1245; 25325</t>
+          <t>1946; 19191</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1358; 26042</t>
+          <t>1928; 17231</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4208; 34831</t>
+          <t>5088; 24838</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>21659</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>24626</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43939</t>
+          <t>46285</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12542; 34717</t>
+          <t>13045; 37047</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14314; 32173</t>
+          <t>17200; 36614</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32087; 61385</t>
+          <t>34138; 63749</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18712</t>
+          <t>18923</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27709</t>
+          <t>28439</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4089; 16822</t>
+          <t>4712; 17429</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12071; 29259</t>
+          <t>12438; 27376</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18983; 39690</t>
+          <t>19518; 39653</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>15788</t>
+          <t>20104</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>23735</t>
+          <t>27166</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39524</t>
+          <t>47269</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8504; 29615</t>
+          <t>10925; 34992</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15151; 35957</t>
+          <t>17733; 41086</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26493; 56147</t>
+          <t>34232; 69996</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>3281</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3710</t>
+          <t>0; 3615</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>315; 3210</t>
+          <t>825; 4628</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>854; 5166</t>
+          <t>1290; 6597</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12177</t>
+          <t>14141</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>26488</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4806; 17081</t>
+          <t>6526; 19475</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6951; 19152</t>
+          <t>8571; 21668</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14467; 30830</t>
+          <t>18817; 37611</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>14181</t>
+          <t>18921</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>36936</t>
+          <t>45588</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>51117</t>
+          <t>64508</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>7626; 24891</t>
+          <t>11032; 31319</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>16216; 56416</t>
+          <t>33514; 59754</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31375; 70823</t>
+          <t>50796; 83661</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>172790</t>
+          <t>203633</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>186875</t>
+          <t>215776</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>359665</t>
+          <t>419409</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>90286; 245475</t>
+          <t>179357; 229772</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>168784; 209958</t>
+          <t>194568; 239054</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>219890; 440421</t>
+          <t>386541; 449832</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>250281</t>
+          <t>293689</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>559326</t>
+          <t>647442</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>195743; 289261</t>
+          <t>261531; 331263</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>252569; 344051</t>
+          <t>322238; 385949</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>481189; 618283</t>
+          <t>599265; 697938</t>
         </is>
       </c>
     </row>
